--- a/data/trans_camb/IP28_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 5,86</t>
+          <t>-2,8; 5,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,31</t>
+          <t>-3,94; 4,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 0,0</t>
+          <t>-7,12; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 1,66</t>
+          <t>-5,89; 1,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,11</t>
+          <t>-5,07; 3,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 3,58</t>
+          <t>-5,39; 3,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,72</t>
+          <t>-3,09; 2,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,92</t>
+          <t>-3,34; 2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,19</t>
+          <t>-4,06; 1,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,63; 236,61</t>
+          <t>-78,58; 225,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 165,41</t>
+          <t>-100,0; 304,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,58</t>
+          <t>-100,0; 234,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,12</t>
+          <t>-0,7; 2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,77</t>
+          <t>-1,7; 0,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,9</t>
+          <t>-1,0; 1,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,05</t>
+          <t>-0,54; 2,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,99</t>
+          <t>-1,24; 1,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,06</t>
+          <t>-1,21; 1,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,67</t>
+          <t>-0,37; 1,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,68</t>
+          <t>-1,11; 0,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,03</t>
+          <t>-0,83; 0,92</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 251,8</t>
+          <t>-42,18; 258,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 119,12</t>
+          <t>-80,25; 89,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 273,67</t>
+          <t>-56,64; 231,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 356,19</t>
+          <t>-44,68; 316,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,12; 174,3</t>
+          <t>-69,76; 205,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 195,75</t>
+          <t>-72,0; 235,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 201,4</t>
+          <t>-23,07; 177,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,85; 78,29</t>
+          <t>-61,92; 71,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 120,47</t>
+          <t>-48,85; 105,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,46</t>
+          <t>-1,51; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,8</t>
+          <t>-1,63; 1,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,7</t>
+          <t>-1,21; 2,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,04</t>
+          <t>-0,42; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,75</t>
+          <t>-1,26; 0,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,7</t>
+          <t>-0,82; 1,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,06</t>
+          <t>-0,57; 1,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,01</t>
+          <t>-1,07; 0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,43</t>
+          <t>-0,81; 1,37</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,36; —</t>
+          <t>-77,13; 1130,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,88</t>
+          <t>-0,42; 1,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,61</t>
+          <t>-1,27; 0,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,39</t>
+          <t>-0,84; 1,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,47</t>
+          <t>-0,53; 1,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,67</t>
+          <t>-1,13; 0,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,66</t>
+          <t>-1,07; 0,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,37</t>
+          <t>-0,19; 1,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,4</t>
+          <t>-0,94; 0,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,66</t>
+          <t>-0,8; 0,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 223,74</t>
+          <t>-24,75; 230,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 81,44</t>
+          <t>-67,71; 78,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,03; 168,86</t>
+          <t>-49,96; 178,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 185,51</t>
+          <t>-35,26; 188,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,43; 96,77</t>
+          <t>-69,31; 85,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,28; 95,07</t>
+          <t>-67,27; 86,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 151,25</t>
+          <t>-15,63; 134,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,61; 46,35</t>
+          <t>-57,04; 36,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,87; 75,9</t>
+          <t>-49,31; 58,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,49</t>
+          <t>-2,32; 5,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 4,6</t>
+          <t>-3,31; 4,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 0,0</t>
+          <t>-5,54; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,7</t>
+          <t>-5,81; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,62</t>
+          <t>-5,04; 3,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 3,04</t>
+          <t>-5,42; 3,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,79</t>
+          <t>-2,55; 2,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,26</t>
+          <t>-3,31; 2,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,45</t>
+          <t>-3,86; 1,34</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,58; 225,18</t>
+          <t>-71,43; 293,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 304,21</t>
+          <t>-100,0; 269,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 234,3</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,37</t>
+          <t>-0,81; 2,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,54</t>
+          <t>-1,7; 0,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,8</t>
+          <t>-1,11; 1,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,02</t>
+          <t>-0,49; 2,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,13</t>
+          <t>-1,22; 1,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,08</t>
+          <t>-1,27; 0,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,57</t>
+          <t>-0,32; 1,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,6</t>
+          <t>-1,08; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,92</t>
+          <t>-0,76; 1,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 258,48</t>
+          <t>-44,29; 316,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,25; 89,13</t>
+          <t>-81,64; 106,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 231,87</t>
+          <t>-59,69; 230,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,68; 316,65</t>
+          <t>-41,99; 320,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,76; 205,51</t>
+          <t>-70,89; 180,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,0; 235,64</t>
+          <t>-77,92; 153,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 177,7</t>
+          <t>-19,9; 212,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,92; 71,7</t>
+          <t>-61,3; 60,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 105,71</t>
+          <t>-44,7; 117,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,07</t>
+          <t>-1,24; 2,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,72</t>
+          <t>-1,26; 1,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,98</t>
+          <t>-1,19; 2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,95</t>
+          <t>-0,41; 3,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,74</t>
+          <t>-1,3; 0,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,45</t>
+          <t>-0,82; 1,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,93</t>
+          <t>-0,59; 1,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,97</t>
+          <t>-1,05; 0,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,37</t>
+          <t>-0,8; 1,43</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,13; 1130,79</t>
+          <t>-78,35; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,95</t>
+          <t>-0,46; 1,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,61</t>
+          <t>-1,31; 0,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,35</t>
+          <t>-1,05; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,46</t>
+          <t>-0,51; 1,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,64</t>
+          <t>-1,08; 0,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,61</t>
+          <t>-1,16; 0,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,33</t>
+          <t>-0,22; 1,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,33</t>
+          <t>-0,89; 0,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,59</t>
+          <t>-0,78; 0,72</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 230,13</t>
+          <t>-24,71; 241,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 78,22</t>
+          <t>-68,68; 70,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 178,96</t>
+          <t>-60,69; 179,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 188,99</t>
+          <t>-35,95; 180,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,31; 85,95</t>
+          <t>-71,16; 81,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,27; 86,53</t>
+          <t>-68,55; 85,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 134,73</t>
+          <t>-13,41; 140,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,04; 36,41</t>
+          <t>-54,83; 49,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,31; 58,94</t>
+          <t>-47,82; 80,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,88</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-1,82</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-1,22</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,72</t>
+          <t>-5,74; 1,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 4,39</t>
+          <t>-5,49; 3,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,0</t>
+          <t>-5,01; 4,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 1,85</t>
+          <t>-2,71; 5,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,76</t>
+          <t>-3,6; 4,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,62</t>
+          <t>-6,2; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,77</t>
+          <t>-2,83; 2,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,4</t>
+          <t>-3,53; 1,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,34</t>
+          <t>-3,79; 1,68</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-48,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-31,98%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-27,36%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>86,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-17,97%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-48,51%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-31,98%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-32,24%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,28%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-53,83%</t>
+          <t>-48,94%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 293,4</t>
+          <t>-74,63; 236,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 269,34</t>
+          <t>-100,0; 165,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 251,43</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,41</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,3</t>
+          <t>-0,62; 2,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,71</t>
+          <t>-1,22; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,82</t>
+          <t>-1,29; 1,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,02</t>
+          <t>-0,8; 2,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,08</t>
+          <t>-1,68; 0,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,98</t>
+          <t>-0,88; 2,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,64</t>
+          <t>-0,24; 1,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,51</t>
+          <t>-0,98; 0,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,05</t>
+          <t>-0,65; 1,24</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56,56%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-6,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-10,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>50,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-29,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21,09%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-6,05%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,04%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 316,43</t>
+          <t>-39,76; 356,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,64; 106,32</t>
+          <t>-71,12; 174,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,69; 230,58</t>
+          <t>-74,52; 193,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 320,96</t>
+          <t>-44,77; 251,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,89; 180,56</t>
+          <t>-79,17; 119,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,92; 153,08</t>
+          <t>-52,61; 312,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 212,13</t>
+          <t>-17,02; 201,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,3; 60,52</t>
+          <t>-58,85; 78,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 117,35</t>
+          <t>-38,91; 147,59</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,05</t>
+          <t>-0,41; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,76</t>
+          <t>-1,26; 0,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,84</t>
+          <t>-0,82; 1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,0</t>
+          <t>-1,2; 2,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,75</t>
+          <t>-1,54; 1,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,49</t>
+          <t>-1,26; 2,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,74</t>
+          <t>-0,55; 2,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,85</t>
+          <t>-1,05; 1,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,43</t>
+          <t>-0,88; 1,6</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>216,18%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-9,16%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>20,54%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>40,51%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>216,18%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-9,16%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,35; —</t>
+          <t>-73,36; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,8</t>
+          <t>-0,59; 1,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,57</t>
+          <t>-1,06; 0,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,32</t>
+          <t>-1,1; 0,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,44</t>
+          <t>-0,39; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,65</t>
+          <t>-1,28; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,64</t>
+          <t>-0,74; 1,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,29</t>
+          <t>-0,19; 1,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,41</t>
+          <t>-0,91; 0,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,72</t>
+          <t>-0,76; 0,81</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34,54%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-19,01%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-18,16%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>53,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-23,6%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-19,01%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-20,28%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-6,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 241,5</t>
+          <t>-36,21; 185,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 70,9</t>
+          <t>-62,43; 96,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,69; 179,59</t>
+          <t>-65,85; 104,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 180,27</t>
+          <t>-28,36; 223,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 81,89</t>
+          <t>-70,93; 81,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 85,55</t>
+          <t>-45,65; 203,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 140,3</t>
+          <t>-12,28; 151,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 49,34</t>
+          <t>-56,61; 46,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 80,38</t>
+          <t>-46,76; 90,58</t>
         </is>
       </c>
     </row>
